--- a/docentes/Rodriguez Roman Marisol - Estadisticos 20241.xlsx
+++ b/docentes/Rodriguez Roman Marisol - Estadisticos 20241.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="31">
   <si>
     <t>Mat</t>
   </si>
@@ -83,6 +83,33 @@
   </si>
   <si>
     <t>Reprobadas</t>
+  </si>
+  <si>
+    <t>BAUTISTA</t>
+  </si>
+  <si>
+    <t>GUERRA</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>DE JESUS</t>
+  </si>
+  <si>
+    <t>JERONIMO</t>
+  </si>
+  <si>
+    <t>ZARATE</t>
+  </si>
+  <si>
+    <t>EDER</t>
+  </si>
+  <si>
+    <t>LUIS</t>
+  </si>
+  <si>
+    <t>OSMAR UZIEL</t>
   </si>
 </sst>
 </file>
@@ -652,16 +679,19 @@
         <v>28</v>
       </c>
       <c r="D2">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>28</v>
+        <v>2</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>92.86</v>
+      </c>
+      <c r="H2">
+        <v>8.199999999999999</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -675,16 +705,19 @@
         <v>10</v>
       </c>
       <c r="D3">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="H3">
+        <v>8.300000000000001</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -698,16 +731,19 @@
         <v>28</v>
       </c>
       <c r="D4">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>28</v>
+        <v>4</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>85.70999999999999</v>
+      </c>
+      <c r="H4">
+        <v>7.4</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -721,16 +757,19 @@
         <v>34</v>
       </c>
       <c r="D5">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>34</v>
+        <v>3</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>91.18000000000001</v>
+      </c>
+      <c r="H5">
+        <v>8.5</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -744,16 +783,19 @@
         <v>34</v>
       </c>
       <c r="D6">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="E6">
-        <v>34</v>
+        <v>1</v>
       </c>
       <c r="F6">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>97.06</v>
+      </c>
+      <c r="H6">
+        <v>8.6</v>
       </c>
     </row>
   </sheetData>
@@ -809,16 +851,16 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F2">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G2">
-        <v>89.29000000000001</v>
+        <v>92.86</v>
       </c>
       <c r="H2">
-        <v>8.199999999999999</v>
+        <v>8.1</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -844,7 +886,7 @@
         <v>100</v>
       </c>
       <c r="H3">
-        <v>8.300000000000001</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -870,7 +912,7 @@
         <v>85.70999999999999</v>
       </c>
       <c r="H4">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -887,16 +929,16 @@
         <v>0</v>
       </c>
       <c r="E5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F5">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G5">
-        <v>94.12</v>
+        <v>91.18000000000001</v>
       </c>
       <c r="H5">
-        <v>8.5</v>
+        <v>8.300000000000001</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -922,7 +964,7 @@
         <v>97.06</v>
       </c>
       <c r="H6">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
     </row>
   </sheetData>
@@ -932,7 +974,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -962,6 +1004,75 @@
         <v>21</v>
       </c>
     </row>
+    <row r="2" spans="1:7">
+      <c r="A2">
+        <v>22330051920006</v>
+      </c>
+      <c r="B2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D2" t="s">
+        <v>28</v>
+      </c>
+      <c r="E2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F2" t="s">
+        <v>14</v>
+      </c>
+      <c r="G2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3">
+        <v>22330051920017</v>
+      </c>
+      <c r="B3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C3" t="s">
+        <v>26</v>
+      </c>
+      <c r="D3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4">
+        <v>22330051920382</v>
+      </c>
+      <c r="B4" t="s">
+        <v>24</v>
+      </c>
+      <c r="C4" t="s">
+        <v>27</v>
+      </c>
+      <c r="D4" t="s">
+        <v>30</v>
+      </c>
+      <c r="E4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F4" t="s">
+        <v>14</v>
+      </c>
+      <c r="G4">
+        <v>2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/docentes/Rodriguez Roman Marisol - Estadisticos 20241.xlsx
+++ b/docentes/Rodriguez Roman Marisol - Estadisticos 20241.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="31">
   <si>
     <t>Mat</t>
   </si>
@@ -467,7 +467,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H6"/>
+  <dimension ref="A1:H5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="50.7109375" customWidth="1"/>
@@ -579,7 +579,7 @@
     </row>
     <row r="5" spans="1:8">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B5" t="s">
         <v>15</v>
@@ -591,41 +591,15 @@
         <v>0</v>
       </c>
       <c r="E5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F5">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G5">
-        <v>94.12</v>
+        <v>97.06</v>
       </c>
       <c r="H5">
-        <v>8.5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8">
-      <c r="A6" t="s">
-        <v>11</v>
-      </c>
-      <c r="B6" t="s">
-        <v>15</v>
-      </c>
-      <c r="C6">
-        <v>34</v>
-      </c>
-      <c r="D6">
-        <v>0</v>
-      </c>
-      <c r="E6">
-        <v>1</v>
-      </c>
-      <c r="F6">
-        <v>33</v>
-      </c>
-      <c r="G6">
-        <v>97.06</v>
-      </c>
-      <c r="H6">
         <v>8.6</v>
       </c>
     </row>
@@ -636,7 +610,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H6"/>
+  <dimension ref="A1:H5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="50.7109375" customWidth="1"/>
@@ -748,7 +722,7 @@
     </row>
     <row r="5" spans="1:8">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B5" t="s">
         <v>15</v>
@@ -760,41 +734,15 @@
         <v>0</v>
       </c>
       <c r="E5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F5">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G5">
-        <v>91.18000000000001</v>
+        <v>97.06</v>
       </c>
       <c r="H5">
-        <v>8.5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8">
-      <c r="A6" t="s">
-        <v>11</v>
-      </c>
-      <c r="B6" t="s">
-        <v>15</v>
-      </c>
-      <c r="C6">
-        <v>34</v>
-      </c>
-      <c r="D6">
-        <v>0</v>
-      </c>
-      <c r="E6">
-        <v>1</v>
-      </c>
-      <c r="F6">
-        <v>33</v>
-      </c>
-      <c r="G6">
-        <v>97.06</v>
-      </c>
-      <c r="H6">
         <v>8.6</v>
       </c>
     </row>
@@ -805,7 +753,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H6"/>
+  <dimension ref="A1:H5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="50.7109375" customWidth="1"/>
@@ -917,7 +865,7 @@
     </row>
     <row r="5" spans="1:8">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B5" t="s">
         <v>15</v>
@@ -929,41 +877,15 @@
         <v>0</v>
       </c>
       <c r="E5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F5">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G5">
-        <v>91.18000000000001</v>
+        <v>97.06</v>
       </c>
       <c r="H5">
-        <v>8.300000000000001</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8">
-      <c r="A6" t="s">
-        <v>11</v>
-      </c>
-      <c r="B6" t="s">
-        <v>15</v>
-      </c>
-      <c r="C6">
-        <v>34</v>
-      </c>
-      <c r="D6">
-        <v>0</v>
-      </c>
-      <c r="E6">
-        <v>1</v>
-      </c>
-      <c r="F6">
-        <v>33</v>
-      </c>
-      <c r="G6">
-        <v>97.06</v>
-      </c>
-      <c r="H6">
         <v>8.199999999999999</v>
       </c>
     </row>

--- a/docentes/Rodriguez Roman Marisol - Estadisticos 20241.xlsx
+++ b/docentes/Rodriguez Roman Marisol - Estadisticos 20241.xlsx
@@ -969,7 +969,7 @@
         <v>14</v>
       </c>
       <c r="G3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -992,7 +992,7 @@
         <v>14</v>
       </c>
       <c r="G4">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/Rodriguez Roman Marisol - Estadisticos 20241.xlsx
+++ b/docentes/Rodriguez Roman Marisol - Estadisticos 20241.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="33">
   <si>
     <t>Mat</t>
   </si>
@@ -85,6 +85,9 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>VIVANCO</t>
+  </si>
+  <si>
     <t>BAUTISTA</t>
   </si>
   <si>
@@ -101,6 +104,9 @@
   </si>
   <si>
     <t>ZARATE</t>
+  </si>
+  <si>
+    <t>LUIS AARON</t>
   </si>
   <si>
     <t>EDER</t>
@@ -896,7 +902,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -928,30 +934,30 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>22330051920006</v>
+        <v>23330051920313</v>
       </c>
       <c r="B2" t="s">
         <v>22</v>
       </c>
       <c r="C2" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="D2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G2">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>22330051920017</v>
+        <v>22330051920006</v>
       </c>
       <c r="B3" t="s">
         <v>23</v>
@@ -960,7 +966,7 @@
         <v>26</v>
       </c>
       <c r="D3" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E3" t="s">
         <v>10</v>
@@ -969,12 +975,12 @@
         <v>14</v>
       </c>
       <c r="G3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920382</v>
+        <v>22330051920017</v>
       </c>
       <c r="B4" t="s">
         <v>24</v>
@@ -983,7 +989,7 @@
         <v>27</v>
       </c>
       <c r="D4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E4" t="s">
         <v>10</v>
@@ -992,6 +998,29 @@
         <v>14</v>
       </c>
       <c r="G4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5">
+        <v>22330051920382</v>
+      </c>
+      <c r="B5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C5" t="s">
+        <v>28</v>
+      </c>
+      <c r="D5" t="s">
+        <v>32</v>
+      </c>
+      <c r="E5" t="s">
+        <v>10</v>
+      </c>
+      <c r="F5" t="s">
+        <v>14</v>
+      </c>
+      <c r="G5">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Rodriguez Roman Marisol - Estadisticos 20241.xlsx
+++ b/docentes/Rodriguez Roman Marisol - Estadisticos 20241.xlsx
@@ -565,10 +565,10 @@
         <v>14</v>
       </c>
       <c r="C4">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E4">
         <v>4</v>
@@ -577,7 +577,7 @@
         <v>24</v>
       </c>
       <c r="G4">
-        <v>85.70999999999999</v>
+        <v>82.76000000000001</v>
       </c>
       <c r="H4">
         <v>7.4</v>
@@ -708,10 +708,10 @@
         <v>14</v>
       </c>
       <c r="C4">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E4">
         <v>4</v>
@@ -720,7 +720,7 @@
         <v>24</v>
       </c>
       <c r="G4">
-        <v>85.70999999999999</v>
+        <v>82.76000000000001</v>
       </c>
       <c r="H4">
         <v>7.4</v>
@@ -851,10 +851,10 @@
         <v>14</v>
       </c>
       <c r="C4">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E4">
         <v>4</v>
@@ -863,7 +863,7 @@
         <v>24</v>
       </c>
       <c r="G4">
-        <v>85.70999999999999</v>
+        <v>82.76000000000001</v>
       </c>
       <c r="H4">
         <v>7.6</v>
@@ -952,7 +952,7 @@
         <v>12</v>
       </c>
       <c r="G2">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:7">

--- a/docentes/Rodriguez Roman Marisol - Estadisticos 20241.xlsx
+++ b/docentes/Rodriguez Roman Marisol - Estadisticos 20241.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="36">
   <si>
     <t>Mat</t>
   </si>
@@ -85,18 +85,24 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>CRUZ</t>
+  </si>
+  <si>
+    <t>BAUTISTA</t>
+  </si>
+  <si>
     <t>VIVANCO</t>
   </si>
   <si>
-    <t>BAUTISTA</t>
-  </si>
-  <si>
     <t>GUERRA</t>
   </si>
   <si>
     <t>MARTINEZ</t>
   </si>
   <si>
+    <t>COYOHUA</t>
+  </si>
+  <si>
     <t>DE JESUS</t>
   </si>
   <si>
@@ -106,10 +112,13 @@
     <t>ZARATE</t>
   </si>
   <si>
+    <t>DIEGO</t>
+  </si>
+  <si>
+    <t>EDER</t>
+  </si>
+  <si>
     <t>LUIS AARON</t>
-  </si>
-  <si>
-    <t>EDER</t>
   </si>
   <si>
     <t>LUIS</t>
@@ -902,7 +911,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -934,25 +943,25 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>23330051920313</v>
+        <v>22330051920010</v>
       </c>
       <c r="B2" t="s">
         <v>22</v>
       </c>
       <c r="C2" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="D2" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="E2" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G2">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -963,10 +972,10 @@
         <v>23</v>
       </c>
       <c r="C3" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D3" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="E3" t="s">
         <v>10</v>
@@ -980,22 +989,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920017</v>
+        <v>23330051920313</v>
       </c>
       <c r="B4" t="s">
         <v>24</v>
       </c>
       <c r="C4" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="D4" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E4" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G4">
         <v>1</v>
@@ -1003,16 +1012,16 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>22330051920382</v>
+        <v>22330051920017</v>
       </c>
       <c r="B5" t="s">
         <v>25</v>
       </c>
       <c r="C5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D5" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E5" t="s">
         <v>10</v>
@@ -1021,6 +1030,29 @@
         <v>14</v>
       </c>
       <c r="G5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6">
+        <v>22330051920382</v>
+      </c>
+      <c r="B6" t="s">
+        <v>26</v>
+      </c>
+      <c r="C6" t="s">
+        <v>30</v>
+      </c>
+      <c r="D6" t="s">
+        <v>35</v>
+      </c>
+      <c r="E6" t="s">
+        <v>10</v>
+      </c>
+      <c r="F6" t="s">
+        <v>14</v>
+      </c>
+      <c r="G6">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Rodriguez Roman Marisol - Estadisticos 20241.xlsx
+++ b/docentes/Rodriguez Roman Marisol - Estadisticos 20241.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="22">
   <si>
     <t>Mat</t>
   </si>
@@ -83,48 +83,6 @@
   </si>
   <si>
     <t>Reprobadas</t>
-  </si>
-  <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
-    <t>BAUTISTA</t>
-  </si>
-  <si>
-    <t>VIVANCO</t>
-  </si>
-  <si>
-    <t>GUERRA</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>COYOHUA</t>
-  </si>
-  <si>
-    <t>DE JESUS</t>
-  </si>
-  <si>
-    <t>JERONIMO</t>
-  </si>
-  <si>
-    <t>ZARATE</t>
-  </si>
-  <si>
-    <t>DIEGO</t>
-  </si>
-  <si>
-    <t>EDER</t>
-  </si>
-  <si>
-    <t>LUIS AARON</t>
-  </si>
-  <si>
-    <t>LUIS</t>
-  </si>
-  <si>
-    <t>OSMAR UZIEL</t>
   </si>
 </sst>
 </file>
@@ -577,16 +535,16 @@
         <v>29</v>
       </c>
       <c r="D4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E4">
         <v>4</v>
       </c>
       <c r="F4">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G4">
-        <v>82.76000000000001</v>
+        <v>86.20999999999999</v>
       </c>
       <c r="H4">
         <v>7.4</v>
@@ -720,16 +678,16 @@
         <v>29</v>
       </c>
       <c r="D4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E4">
         <v>4</v>
       </c>
       <c r="F4">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G4">
-        <v>82.76000000000001</v>
+        <v>86.20999999999999</v>
       </c>
       <c r="H4">
         <v>7.4</v>
@@ -814,16 +772,16 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F2">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G2">
-        <v>92.86</v>
+        <v>96.43000000000001</v>
       </c>
       <c r="H2">
-        <v>8.1</v>
+        <v>8.300000000000001</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -863,19 +821,19 @@
         <v>29</v>
       </c>
       <c r="D4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F4">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="G4">
-        <v>82.76000000000001</v>
+        <v>100</v>
       </c>
       <c r="H4">
-        <v>7.6</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -892,16 +850,16 @@
         <v>0</v>
       </c>
       <c r="E5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F5">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G5">
-        <v>97.06</v>
+        <v>100</v>
       </c>
       <c r="H5">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
     </row>
   </sheetData>
@@ -911,7 +869,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -941,121 +899,6 @@
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
-      <c r="A2">
-        <v>22330051920010</v>
-      </c>
-      <c r="B2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C2" t="s">
-        <v>27</v>
-      </c>
-      <c r="D2" t="s">
-        <v>31</v>
-      </c>
-      <c r="E2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F2" t="s">
-        <v>14</v>
-      </c>
-      <c r="G2">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3">
-        <v>22330051920006</v>
-      </c>
-      <c r="B3" t="s">
-        <v>23</v>
-      </c>
-      <c r="C3" t="s">
-        <v>28</v>
-      </c>
-      <c r="D3" t="s">
-        <v>32</v>
-      </c>
-      <c r="E3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F3" t="s">
-        <v>14</v>
-      </c>
-      <c r="G3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4">
-        <v>23330051920313</v>
-      </c>
-      <c r="B4" t="s">
-        <v>24</v>
-      </c>
-      <c r="C4" t="s">
-        <v>24</v>
-      </c>
-      <c r="D4" t="s">
-        <v>33</v>
-      </c>
-      <c r="E4" t="s">
-        <v>8</v>
-      </c>
-      <c r="F4" t="s">
-        <v>12</v>
-      </c>
-      <c r="G4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5">
-        <v>22330051920017</v>
-      </c>
-      <c r="B5" t="s">
-        <v>25</v>
-      </c>
-      <c r="C5" t="s">
-        <v>29</v>
-      </c>
-      <c r="D5" t="s">
-        <v>34</v>
-      </c>
-      <c r="E5" t="s">
-        <v>10</v>
-      </c>
-      <c r="F5" t="s">
-        <v>14</v>
-      </c>
-      <c r="G5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6">
-        <v>22330051920382</v>
-      </c>
-      <c r="B6" t="s">
-        <v>26</v>
-      </c>
-      <c r="C6" t="s">
-        <v>30</v>
-      </c>
-      <c r="D6" t="s">
-        <v>35</v>
-      </c>
-      <c r="E6" t="s">
-        <v>10</v>
-      </c>
-      <c r="F6" t="s">
-        <v>14</v>
-      </c>
-      <c r="G6">
-        <v>1</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
